--- a/output/pdf_financials_xlsx/TNO.H.xlsx
+++ b/output/pdf_financials_xlsx/TNO.H.xlsx
@@ -5874,40 +5874,40 @@
         <v>1.353387</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.353387</v>
+        <v>1.717031</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.162571</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.273441</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.287014</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.287014</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.287014</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.356287</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.423553</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.413848</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.481838</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.675427</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.1199</v>
       </c>
       <c r="P92" s="3" t="n">
         <v>0</v>
@@ -10352,7 +10352,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10651,7 +10655,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11419,7 +11427,11 @@
           <t>Warrant reserve 9</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12286,7 +12298,11 @@
           <t>Warrant reserve 9</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12985,7 +13001,11 @@
           <t>Warrant reserve 10</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -14064,7 +14084,11 @@
           <t>Warrant reserve 11</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -14856,7 +14880,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -16246,7 +16274,11 @@
           <t>Warrant reserve 14</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -16737,7 +16769,11 @@
           <t>Warrant reserve 14</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -17333,7 +17369,11 @@
           <t>Warrants reserves 13</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TNO.H.xlsx
+++ b/output/pdf_financials_xlsx/TNO.H.xlsx
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.030185</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004048</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.009658</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.287267</v>
+        <v>-1.317452</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.988437</v>
+        <v>-0.992485</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.406196</v>
+        <v>-1.415854</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.772969</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.287267</v>
+        <v>-1.317452</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.988437</v>
+        <v>-0.992485</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.406196</v>
+        <v>-1.415854</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.772969</v>
@@ -2430,31 +2430,31 @@
         <v>0.03541</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.030809</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.420659</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.017838</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.019041</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.15337</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.193473</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.165293</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.035882</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.033219</v>
       </c>
     </row>
     <row r="35">
@@ -2546,31 +2546,31 @@
         <v>0.03541</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.030809</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.420659</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.017838</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.019041</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.15337</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.193473</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.165293</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.035882</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.033219</v>
       </c>
     </row>
     <row r="37">
@@ -3242,31 +3242,31 @@
         <v>0.045099</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.034434</v>
+        <v>0.003625</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.424809</v>
+        <v>0.00415</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.028416</v>
+        <v>0.010578</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.019557</v>
+        <v>0.000516</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.173886</v>
+        <v>0.020516</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.248233</v>
+        <v>0.05476</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.16992</v>
+        <v>0.004627</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.047809</v>
+        <v>0.011927</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.03889</v>
+        <v>0.005671</v>
       </c>
     </row>
     <row r="49">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -47337,7 +47337,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -56373,7 +56373,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -59209,7 +59209,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E510" s="5" t="n">

--- a/output/pdf_financials_xlsx/TNO.H.xlsx
+++ b/output/pdf_financials_xlsx/TNO.H.xlsx
@@ -1303,7 +1303,7 @@
         <v>-0.371972</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.596922</v>
+        <v>-0.5601930000000001</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>-0.296099</v>
@@ -1361,7 +1361,7 @@
         <v>-0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.036729</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>-0</v>
@@ -2025,7 +2025,7 @@
         <v>-0.371972</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.596922</v>
+        <v>-0.5601930000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-0.296099</v>
@@ -2141,7 +2141,7 @@
         <v>-0.371972</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.596922</v>
+        <v>-0.5601930000000001</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-0.296099</v>
@@ -2291,7 +2291,7 @@
         <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0</v>
+        <v>-6.556490352432108</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>-0</v>
@@ -7095,10 +7095,10 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.516729</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.114885</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>-0.499884</v>
@@ -7162,10 +7162,10 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.49985</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -27613,7 +27613,11 @@
           <t>Issuance of shares and warrants on private placement</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -30694,7 +30698,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -32924,7 +32932,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -33940,7 +33952,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E257" s="5" t="n">
         <v>-0.516729</v>
       </c>
@@ -37480,7 +37496,11 @@
           <t>Income tax recovery 12</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
